--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
@@ -620,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -674,11 +674,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1233,62 +1233,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nijel Pack</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1315,68 +1315,68 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Denzel Aberdeen</t>
+          <t>Nijel Pack</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1494,11 +1494,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
@@ -1522,19 +1522,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1576,14 +1576,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1598,13 +1598,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2093,10 +2093,10 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -2503,10 +2503,10 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -2588,13 +2588,13 @@
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2670,19 +2670,19 @@
         <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -2916,13 +2916,13 @@
         <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -2970,18 +2970,18 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>6</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>5</v>
-      </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -3162,25 +3162,25 @@
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
@@ -3311,7 +3311,7 @@
         <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -3380,14 +3380,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3408,19 +3408,19 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
+        <v>6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
         <v>5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
         <v>3</v>
@@ -3490,19 +3490,19 @@
         <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3651,10 +3651,10 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -3708,11 +3708,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I40" t="n">
         <v>14</v>
@@ -3736,19 +3736,19 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
         <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3876,13 +3876,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I42" t="n">
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q42" t="n">
         <v>8</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4185,62 +4185,62 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Pop Isaacs</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4267,62 +4267,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pop Isaacs</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q47" t="n">
         <v>4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>4</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2</v>
       </c>
       <c r="R47" t="n">
         <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Ali Dibba</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="n">
         <v>6</v>
       </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>2</v>
@@ -4386,13 +4386,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
@@ -4401,16 +4401,16 @@
         <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4431,68 +4431,68 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
         <v>5</v>
       </c>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
         <v>4</v>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>London Jemison</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4535,34 +4535,34 @@
         <v>5</v>
       </c>
       <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4595,44 +4595,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ali Dibba</t>
+          <t>London Jemison</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
         <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -4644,13 +4644,13 @@
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>2</v>
@@ -4677,68 +4677,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H52" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
         <v>4</v>
       </c>
-      <c r="I52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>3</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>8</v>
-      </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -4759,22 +4759,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4784,10 +4784,10 @@
         <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -4799,22 +4799,22 @@
         <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
         <v>8</v>
       </c>
-      <c r="Q53" t="n">
-        <v>3</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="n">
         <v>4</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4841,53 +4841,53 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
         <v>4</v>
@@ -4899,10 +4899,10 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -5786,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -5907,22 +5907,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5944,13 +5944,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -5962,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5989,29 +5989,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -6029,16 +6029,16 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -6071,32 +6071,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6111,28 +6111,28 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6153,22 +6153,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -6178,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6193,22 +6193,22 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6235,12 +6235,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Zach Clemence</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6250,17 +6250,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:20 - 1st Half</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P71" t="n">
         <v>7</v>
@@ -6284,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -6293,10 +6293,10 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -6317,35 +6317,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Zach Clemence</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4:57 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -6354,31 +6354,31 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0:49 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>5:01 - 1st Half</t>
+          <t>3:31 - 1st Half</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -6761,27 +6761,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V131"/>
+  <dimension ref="A1:V134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -674,17 +674,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -696,13 +696,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -741,68 +741,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Derrion Reid</t>
+          <t>Pablo Tamba</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -823,68 +823,68 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>James Scott</t>
+          <t>Derrion Reid</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
         <v>6</v>
       </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -905,56 +905,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pablo Tamba</t>
+          <t>James Scott</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1412,53 +1412,53 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1904,41 +1904,41 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -1947,10 +1947,10 @@
         <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1971,68 +1971,68 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aden Holloway</t>
+          <t>Keyshawn Hall</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2053,17 +2053,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mark Mitchell</t>
+          <t>Aden Holloway</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="R20" t="n">
-        <v>6</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2135,68 +2135,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Keyshawn Hall</t>
+          <t>Mark Mitchell</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2217,68 +2217,68 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Collin Chandler</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2299,68 +2299,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Collin Chandler</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2396,53 +2396,53 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
         <v>5</v>
       </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4</v>
-      </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -3052,20 +3052,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3</v>
-      </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3074,20 +3074,20 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
@@ -3095,10 +3095,10 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3447,68 +3447,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -3529,32 +3529,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
         <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -3566,31 +3566,31 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3775,68 +3775,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Malachi Moreno</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H41" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>16</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="n">
-        <v>5</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="R41" t="n">
+        <v>17</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>9</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
+      </c>
+      <c r="V41" t="n">
         <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4</v>
-      </c>
-      <c r="P41" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3857,17 +3857,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Amari Allen</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3876,49 +3876,49 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -3939,47 +3939,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Amari Allen</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I43" t="n">
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P43" t="n">
         <v>21</v>
@@ -3988,19 +3988,19 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>4</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4185,65 +4185,65 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Xzayvier Brown</t>
+          <t>Kevin Overton</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I46" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" t="n">
+        <v>10</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
         <v>5</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3</v>
-      </c>
-      <c r="P46" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4</v>
-      </c>
-      <c r="R46" t="n">
-        <v>8</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>5</v>
@@ -4282,20 +4282,20 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4304,19 +4304,19 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -4325,10 +4325,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
@@ -4349,68 +4349,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kevin Overton</t>
+          <t>Xzayvier Brown</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -5184,53 +5184,53 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P58" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R58" t="n">
+        <v>19</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9</v>
+      </c>
+      <c r="V58" t="n">
         <v>12</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="n">
-        <v>5</v>
-      </c>
-      <c r="U58" t="n">
-        <v>2</v>
-      </c>
-      <c r="V58" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -5376,7 +5376,7 @@
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q60" t="n">
         <v>4</v>
@@ -5512,20 +5512,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I62" t="n">
         <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -5537,22 +5537,22 @@
         <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P62" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
         <v>6</v>
       </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
       <c r="S62" t="n">
         <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5579,38 +5579,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rubén Dominguez</t>
+          <t>Tahaad Pettiford</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -5619,28 +5619,28 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R63" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -5661,50 +5661,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tae Davis</t>
+          <t>Elyjah Freeman</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
+        <v>14</v>
+      </c>
+      <c r="I64" t="n">
         <v>10</v>
       </c>
-      <c r="I64" t="n">
-        <v>12</v>
-      </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
@@ -5713,16 +5713,16 @@
         <v>6</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5743,35 +5743,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Rubén Dominguez</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5783,22 +5783,22 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5825,68 +5825,68 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tahaad Pettiford</t>
+          <t>Tae Davis</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P66" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -5907,35 +5907,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Elyjah Freeman</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5944,25 +5944,25 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6071,68 +6071,68 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Pop Isaacs</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>20</v>
       </c>
       <c r="I69" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>8</v>
-      </c>
-      <c r="L69" t="n">
-        <v>2</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>3</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7</v>
-      </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -6153,65 +6153,65 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Pop Isaacs</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V70" t="n">
         <v>6</v>
@@ -6235,68 +6235,68 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I71" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P71" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T71" t="n">
         <v>5</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -6317,68 +6317,68 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Zach Clemence</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P72" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q72" t="n">
         <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -6399,17 +6399,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ali Dibba</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6418,49 +6418,49 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -6481,17 +6481,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Zach Clemence</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6500,49 +6500,49 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P74" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Q74" t="n">
         <v>3</v>
       </c>
       <c r="R74" t="n">
+        <v>8</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="n">
         <v>6</v>
       </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -6563,17 +6563,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Ali Dibba</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6588,13 +6588,13 @@
         <v>8</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6603,28 +6603,28 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
         <v>4</v>
       </c>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CJ Ingram</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6664,49 +6664,49 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -6727,38 +6727,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -6767,22 +6767,22 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>CJ Ingram</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6831,13 +6831,13 @@
         <v>11</v>
       </c>
       <c r="I78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -6849,22 +6849,22 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Q78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -6891,35 +6891,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J79" t="n">
         <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -6928,25 +6928,25 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7137,29 +7137,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>PJ Carter</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H82" t="n">
         <v>10</v>
       </c>
       <c r="I82" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>2</v>
@@ -7174,25 +7174,25 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -7219,17 +7219,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7238,49 +7238,49 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I83" t="n">
+        <v>11</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>3</v>
+      </c>
+      <c r="P83" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>4</v>
+      </c>
+      <c r="R83" t="n">
+        <v>8</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3</v>
+      </c>
+      <c r="T83" t="n">
         <v>7</v>
       </c>
-      <c r="J83" t="n">
-        <v>3</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>2</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>3</v>
-      </c>
-      <c r="R83" t="n">
-        <v>3</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7301,68 +7301,68 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>9</v>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -7383,17 +7383,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7405,7 +7405,7 @@
         <v>9</v>
       </c>
       <c r="I85" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>3</v>
@@ -7414,37 +7414,37 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7487,46 +7487,46 @@
         <v>9</v>
       </c>
       <c r="I86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P86" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -7547,68 +7547,68 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I87" t="n">
+        <v>9</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>12</v>
       </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>3</v>
-      </c>
-      <c r="O87" t="n">
-        <v>2</v>
-      </c>
-      <c r="P87" t="n">
-        <v>28</v>
-      </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S87" t="n">
         <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -7629,17 +7629,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7648,49 +7648,49 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I88" t="n">
+        <v>9</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
         <v>5</v>
       </c>
-      <c r="J88" t="n">
+      <c r="S88" t="n">
+        <v>2</v>
+      </c>
+      <c r="T88" t="n">
         <v>5</v>
       </c>
-      <c r="K88" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>2</v>
-      </c>
-      <c r="P88" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>2</v>
-      </c>
-      <c r="R88" t="n">
-        <v>3</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Josh Holloway</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7730,49 +7730,49 @@
         </is>
       </c>
       <c r="H89" t="n">
+        <v>9</v>
+      </c>
+      <c r="I89" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>3</v>
+      </c>
+      <c r="P89" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>3</v>
+      </c>
+      <c r="R89" t="n">
         <v>8</v>
       </c>
-      <c r="I89" t="n">
-        <v>5</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="P89" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" t="n">
-        <v>2</v>
-      </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -7793,68 +7793,68 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H90" t="n">
         <v>8</v>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>5</v>
+      </c>
+      <c r="R90" t="n">
         <v>10</v>
       </c>
-      <c r="Q90" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" t="n">
-        <v>2</v>
-      </c>
       <c r="S90" t="n">
         <v>2</v>
       </c>
       <c r="T90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7875,17 +7875,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7894,16 +7894,16 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -7912,19 +7912,19 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V91" t="n">
         <v>4</v>
@@ -7957,17 +7957,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>King Grace</t>
+          <t>Josh Holloway</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7976,46 +7976,46 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Q92" t="n">
         <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V92" t="n">
         <v>2</v>
@@ -8039,17 +8039,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8058,16 +8058,16 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -8076,31 +8076,31 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
         <v>19</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>King Grace</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J94" t="n">
         <v>3</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
         <v>2</v>
       </c>
       <c r="P94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q94" t="n">
         <v>2</v>
@@ -8173,16 +8173,16 @@
         <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8225,13 +8225,13 @@
         <v>6</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -8240,25 +8240,25 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P95" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Viktor Mikic</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8304,13 +8304,13 @@
         </is>
       </c>
       <c r="H96" t="n">
+        <v>6</v>
+      </c>
+      <c r="I96" t="n">
         <v>5</v>
       </c>
-      <c r="I96" t="n">
-        <v>2</v>
-      </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
         <v>2</v>
@@ -8322,25 +8322,25 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P96" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -8367,36 +8367,36 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Jalen Reece</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I97" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
         <v>5</v>
       </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
@@ -8404,31 +8404,31 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T97" t="n">
         <v>3</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -8449,17 +8449,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8468,43 +8468,43 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Q98" t="n">
         <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -8531,32 +8531,32 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cooper Josefsberg</t>
+          <t>Robert Miller III</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -8565,34 +8565,34 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
         <v>2</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>Viktor Mikic</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8632,16 +8632,16 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I100" t="n">
         <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -8656,13 +8656,13 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q100" t="n">
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -8695,35 +8695,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -8738,19 +8738,19 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -8777,17 +8777,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>London Jemison</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8796,19 +8796,19 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -8817,28 +8817,28 @@
         <v>2</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Cooper Josefsberg</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -8896,25 +8896,25 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -8941,68 +8941,68 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Sebastian Williams-Adams</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P104" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -9023,26 +9023,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
         <v>2</v>
@@ -9051,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -9060,13 +9060,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -9105,56 +9105,56 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Federiko Federiko</t>
+          <t>Filip Jovic</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
         <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -9187,32 +9187,32 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
@@ -9230,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
@@ -9239,10 +9239,10 @@
         <v>2</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -9269,56 +9269,56 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Jalen Reece</t>
+          <t>London Jemison</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -9327,10 +9327,10 @@
         <v>1</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -9351,17 +9351,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Jasper Johnson</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9370,16 +9370,16 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -9388,25 +9388,25 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P109" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q109" t="n">
         <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -9433,35 +9433,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Koren Johnson</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H110" t="n">
         <v>2</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -9473,13 +9473,13 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
         <v>1</v>
@@ -9488,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -9515,22 +9515,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Federiko Federiko</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -9540,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -9552,13 +9552,13 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P111" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -9576,7 +9576,7 @@
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Christ Essandoko</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9616,13 +9616,13 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -9631,28 +9631,28 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Jasper Johnson</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9698,16 +9698,16 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -9716,31 +9716,31 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P113" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -9761,35 +9761,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Koren Johnson</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -9801,28 +9801,28 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -9843,35 +9843,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -9886,19 +9886,19 @@
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -9940,11 +9940,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -10007,26 +10007,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Christ Essandoko</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>12:44 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -10035,34 +10035,34 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -10089,17 +10089,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Eli Sparkman</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10108,16 +10108,16 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -10126,31 +10126,31 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -10171,68 +10171,68 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Rashad King</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
         <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10293,28 +10293,28 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10354,16 +10354,16 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -10375,22 +10375,22 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -10417,68 +10417,68 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Olivier Rioux</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P122" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -10499,22 +10499,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sebastian Williams-Adams</t>
+          <t>Eli Sparkman</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -10581,17 +10581,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Alex Lloyd</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10600,13 +10600,13 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -10621,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -10663,17 +10663,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Dellquan Warren</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10682,13 +10682,13 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -10706,13 +10706,13 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -10745,17 +10745,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10779,34 +10779,34 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P126" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Filip Jovic</t>
+          <t>Mazi Mosley</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10842,11 +10842,11 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>2:51 - 2nd Half</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -10858,13 +10858,13 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -10909,17 +10909,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Olivier Rioux</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -10946,13 +10946,13 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -10991,22 +10991,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Robert Miller III</t>
+          <t>Alex Lloyd</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>14:27 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -11028,25 +11028,25 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -11073,12 +11073,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Alex Kovatchev</t>
+          <t>Dellquan Warren</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -11116,19 +11116,19 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -11155,67 +11155,313 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>Elijah Strong</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>TENN@SC</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" t="n">
+        <v>3</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Noah Williamson</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ALA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ALA@UGA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Alex Kovatchev</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MSST@FLA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>2</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>Eli Ellis</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>TENN@SC</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="H131" t="n">
+      <c r="H134" t="n">
         <v>-2</v>
       </c>
-      <c r="I131" t="n">
-        <v>2</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
+      <c r="I134" t="n">
+        <v>2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
         <v>15</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>4</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" t="n">
-        <v>2</v>
-      </c>
-      <c r="V131" t="n">
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2</v>
+      </c>
+      <c r="V134" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11258,27 +11504,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -11288,7 +11534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -11301,7 +11547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -11310,27 +11556,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11340,7 +11586,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V134"/>
+  <dimension ref="A1:V136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -772,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -784,19 +784,19 @@
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
         <v>3</v>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
         <v>6</v>
@@ -2008,31 +2008,31 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>12</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" t="n">
-        <v>11</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3080,7 +3080,7 @@
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="n">
         <v>4</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4228,7 +4228,7 @@
         <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q46" t="n">
         <v>6</v>
@@ -4282,17 +4282,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -4307,10 +4307,10 @@
         <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
@@ -4325,10 +4325,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V47" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
         <v>2</v>
@@ -5619,10 +5619,10 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q63" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
         <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -5676,23 +5676,23 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>1</v>
@@ -5704,7 +5704,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Jalen Reece</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7077,13 +7077,13 @@
         <v>10</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
@@ -7092,31 +7092,31 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O81" t="n">
         <v>2</v>
       </c>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
+        <v>8</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>4</v>
+      </c>
+      <c r="V81" t="n">
         <v>5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -7137,29 +7137,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PJ Carter</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H82" t="n">
         <v>10</v>
       </c>
       <c r="I82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J82" t="n">
         <v>2</v>
@@ -7174,16 +7174,16 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P82" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R82" t="n">
         <v>5</v>
@@ -7192,7 +7192,7 @@
         <v>2</v>
       </c>
       <c r="T82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -7219,17 +7219,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>PJ Carter</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7241,7 +7241,7 @@
         <v>10</v>
       </c>
       <c r="I83" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J83" t="n">
         <v>2</v>
@@ -7256,25 +7256,25 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R83" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -7301,38 +7301,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -7341,28 +7341,28 @@
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P84" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7383,68 +7383,68 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H85" t="n">
         <v>9</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q85" t="n">
         <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7487,13 +7487,13 @@
         <v>9</v>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -7505,22 +7505,22 @@
         <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>1</v>
@@ -7547,68 +7547,68 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H87" t="n">
         <v>9</v>
       </c>
       <c r="I87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q87" t="n">
         <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
         <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -7629,22 +7629,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -7654,10 +7654,10 @@
         <v>9</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -7666,10 +7666,10 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
         <v>12</v>
@@ -7678,13 +7678,13 @@
         <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S88" t="n">
         <v>2</v>
       </c>
       <c r="T88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
         <v>3</v>
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7733,16 +7733,16 @@
         <v>9</v>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -7751,22 +7751,22 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U89" t="n">
         <v>3</v>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7812,49 +7812,49 @@
         </is>
       </c>
       <c r="H90" t="n">
+        <v>9</v>
+      </c>
+      <c r="I90" t="n">
+        <v>10</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>3</v>
+      </c>
+      <c r="P90" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>3</v>
+      </c>
+      <c r="R90" t="n">
         <v>8</v>
       </c>
-      <c r="I90" t="n">
-        <v>12</v>
-      </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>3</v>
-      </c>
-      <c r="O90" t="n">
-        <v>2</v>
-      </c>
-      <c r="P90" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>5</v>
-      </c>
-      <c r="R90" t="n">
-        <v>10</v>
-      </c>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7897,46 +7897,46 @@
         <v>8</v>
       </c>
       <c r="I91" t="n">
+        <v>12</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2</v>
+      </c>
+      <c r="P91" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q91" t="n">
         <v>5</v>
       </c>
-      <c r="J91" t="n">
-        <v>5</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2</v>
-      </c>
-      <c r="P91" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>2</v>
-      </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7957,17 +7957,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Josh Holloway</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UK@TA&amp;M</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7982,13 +7982,13 @@
         <v>5</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -7997,16 +7997,16 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P92" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Q92" t="n">
         <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="V92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -8039,17 +8039,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Josh Holloway</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>UK@TA&amp;M</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8058,34 +8058,34 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
         <v>2</v>
@@ -8097,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>King Grace</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8143,13 +8143,13 @@
         <v>7</v>
       </c>
       <c r="I94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -8158,31 +8158,31 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>King Grace</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8222,16 +8222,16 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J95" t="n">
         <v>3</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -8240,31 +8240,31 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8307,13 +8307,13 @@
         <v>6</v>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>3</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -8322,22 +8322,22 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P96" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
         <v>3</v>
@@ -8367,35 +8367,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Jalen Reece</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H97" t="n">
         <v>6</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -8404,31 +8404,31 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P97" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="Q97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
         <v>3</v>
       </c>
       <c r="U97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9230,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
@@ -9843,32 +9843,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Mazi Mosley</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H115" t="n">
         <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -9883,22 +9883,22 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -9925,38 +9925,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Blake Muschalek</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -10007,17 +10007,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Christ Essandoko</t>
+          <t>Blake Muschalek</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10032,13 +10032,13 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -10089,17 +10089,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Christ Essandoko</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10111,13 +10111,13 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -10126,31 +10126,31 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="Q118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -10171,38 +10171,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Rashad King</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H119" t="n">
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -10214,25 +10214,25 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Rashad King</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIZ@OU</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10278,31 +10278,31 @@
         <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MIZ@OU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10357,13 +10357,13 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -10378,25 +10378,25 @@
         <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -10417,29 +10417,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>VAN@MISS</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
@@ -10448,37 +10448,37 @@
         <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -10499,68 +10499,68 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Eli Sparkman</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>VAN@MISS</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P123" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -10581,17 +10581,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Eli Sparkman</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10606,7 +10606,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -10621,22 +10621,22 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -10663,17 +10663,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>1</v>
@@ -10703,16 +10703,16 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -10745,17 +10745,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -10767,10 +10767,10 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -10785,28 +10785,28 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -10827,22 +10827,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mazi Mosley</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LSU@AUB</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2:51 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -10867,10 +10867,10 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P127" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -10991,17 +10991,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Alex Lloyd</t>
+          <t>Reed Trapp</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>LSU@AUB</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -11034,19 +11034,19 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -11073,12 +11073,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Dellquan Warren</t>
+          <t>Alex Lloyd</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Dellquan Warren</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11177,7 +11177,7 @@
         <v>-1</v>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -11198,25 +11198,25 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -11237,17 +11237,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ALA@UGA</t>
+          <t>TENN@SC</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11259,7 +11259,7 @@
         <v>-1</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11271,34 +11271,34 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -11319,17 +11319,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Alex Kovatchev</t>
+          <t>Noah Williamson</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MSST@FLA</t>
+          <t>ALA@UGA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P133" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -11401,17 +11401,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Alex Kovatchev</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>TENN@SC</t>
+          <t>MSST@FLA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11423,7 +11423,7 @@
         <v>-2</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11444,24 +11444,188 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>2</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CJ Williams</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AUB</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>LSU@AUB</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Eli Ellis</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>TENN@SC</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
         <v>15</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>4</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" t="n">
-        <v>2</v>
-      </c>
-      <c r="V134" t="n">
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>4</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2</v>
+      </c>
+      <c r="V136" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11547,7 +11711,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-03.xlsx
@@ -7262,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q83" t="n">
         <v>3</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
